--- a/previsionnel_2026.xlsx
+++ b/previsionnel_2026.xlsx
@@ -507,10 +507,10 @@
         <v>2026</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>56618.68</v>
+        <v>56751.68</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12284.62</v>
+        <v>12351.12</v>
       </c>
     </row>
   </sheetData>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1586,31 +1586,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PDMDEP-29485</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-133</v>
+        <v>548.4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         <v>0.5</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-66.5</v>
+        <v>274.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-33207</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>LiExp - Crédits d'heure + TDC MV</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1651,24 +1651,24 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>548.4</v>
+        <v>184.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Basse</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>274.2</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PDMDEP-33207</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LiExp - Crédits d'heure + TDC MV</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1692,24 +1692,24 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>184.5</v>
+        <v>657.3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Basse</t>
+          <t>Non planifié</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>27.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>657.3</v>
+        <v>1890</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1890</v>
+        <v>1000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1000</v>
+        <v>895</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>895</v>
+        <v>171.4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>171.4</v>
+        <v>205.68</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>205.68</v>
+        <v>171.4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PDMDEP-33352</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>171.4</v>
+        <v>705</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>705</v>
+        <v>564</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>564</v>
+        <v>460</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2078,48 +2078,48 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Non planifié</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-33465</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>Mairie de Buis-les-baronnies</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>INITIATION GEODP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2143,39 +2143,39 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Non planifié</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PDMDEP-33465</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mairie de Buis-les-baronnies</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INITIATION GEODP</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>450</v>
+        <v>1242.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1242.5</v>
+        <v>1365</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1365</v>
+        <v>4040</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2283,48 +2283,48 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>4040</v>
+        <v>3288.55</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Non planifié</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>1644.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Pastell + Reprise</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2348,24 +2348,24 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3288.55</v>
+        <v>1790</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>1644.28</v>
+        <v>1521.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BOBIGNY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pastell + Reprise</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2389,24 +2389,24 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1790</v>
+        <v>2812.32</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1521.5</v>
+        <v>1406.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Modélisation + Redevances</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2430,24 +2430,24 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2812.32</v>
+        <v>1556.25</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>1406.16</v>
+        <v>1322.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Modélisation + Redevances</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2471,24 +2471,24 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1556.25</v>
+        <v>2323</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>1322.81</v>
+        <v>1161.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2512,24 +2512,24 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2323</v>
+        <v>1212</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Haute</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1161.5</v>
+        <v>1030.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1212</v>
+        <v>732</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2564,13 +2564,13 @@
         <v>0.85</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>1030.2</v>
+        <v>622.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>CP + Directeur de projet</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>732</v>
+        <v>392.5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2605,13 +2605,13 @@
         <v>0.85</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>622.2</v>
+        <v>333.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CP + Directeur de projet</t>
+          <t>Pack Vision</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>392.5</v>
+        <v>350</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2646,13 +2646,13 @@
         <v>0.85</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>333.62</v>
+        <v>297.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pack Vision</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2687,13 +2687,13 @@
         <v>0.85</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>297.5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2717,24 +2717,24 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>120</v>
+        <v>1250</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Haute</t>
+          <t>Non planifié</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2000</v>
+        <v>882.5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>882.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1046.5</v>
+        <v>440.38</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>440.38</v>
+        <v>2650</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Flux communication</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>2650</v>
+        <v>157.5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Flux communication</t>
+          <t>MAJ carto</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>157.5</v>
+        <v>250</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3062,22 +3062,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>CASTELNAUDARY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
+          <t>Interfaces Littéralis Standard</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3086,24 +3086,24 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>250</v>
+        <v>510.6</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Non planifié</t>
+          <t>Moyenne</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>255.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-32829</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CASTELNAUDARY</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Interfaces Littéralis Standard</t>
+          <t>Mise en service Littéralis Standard</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3127,24 +3127,24 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>510.6</v>
+        <v>50</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moyenne</t>
+          <t>Non planifié</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>255.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mise en service Littéralis Standard</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>50</v>
+        <v>71.2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3182,211 +3182,170 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>PDMDEP-31289</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Valentin CAUJOLLE</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>COMMUNE DE LUNEL</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Non planifié</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="E70" s="6" t="inlineStr">
+    <row r="69">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>TOTAL GÉNÉRAL</t>
         </is>
       </c>
-      <c r="F70" s="7" t="n">
-        <v>56618.68</v>
-      </c>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
-      <c r="I70" s="7" t="n">
-        <v>12284.62</v>
+      <c r="F69" s="7" t="n">
+        <v>56751.68</v>
+      </c>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="7" t="n">
+        <v>12351.12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par CP</t>
+        </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Sous-totaux par CP</t>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Prévision brute (€)</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Prévision pondérée (€)</t>
-        </is>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>23853.5</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>9441.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>23853.5</v>
+        <v>17586.2</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>9441.77</v>
+        <v>2287.17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>17453.2</v>
+        <v>7452.68</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2220.67</v>
+        <v>301.88</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>7452.68</v>
+        <v>631.8</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>301.88</v>
+        <v>255.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>631.8</v>
+        <v>580</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>255.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>580</v>
+        <v>6647.5</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Quentin BORDILLON</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>6647.5</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par solution</t>
+        </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Sous-totaux par solution</t>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Prévision brute (€)</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Prévision pondérée (€)</t>
-        </is>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>24813.7</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>2352.17</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>24680.7</v>
+        <v>31937.98</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2285.67</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>31937.98</v>
-      </c>
-      <c r="C84" s="3" t="n">
         <v>9998.950000000001</v>
       </c>
     </row>

--- a/previsionnel_2026.xlsx
+++ b/previsionnel_2026.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Récap" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Juillet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Août" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -511,6 +512,22 @@
       </c>
       <c r="D4" s="3" t="n">
         <v>12351.12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>61735.89</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>10014.31</v>
       </c>
     </row>
   </sheetData>
@@ -3352,4 +3369,2909 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Prévisionnel pondéré — Août 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Capturé le 01/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Ticket CA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Niveau de confiance</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PDMDEP-34117</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMMUNE DU PUY EN VELAY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier + migration ODP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>707</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PDMDEP-32161</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CAVAILLON</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PDMDEP-33440</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4174</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PDMDEP-33526</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VILLE DE MONTREUIL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1416</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PDMDEP-33272</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CAPBRETON</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PDMDEP-28310</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>362.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32470</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NANTES METROPOLE - VDC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2335</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>350.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31658</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE GUILLESTRE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GeoDP Placier</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>172.97</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COMMUNE DE GRASSE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1079</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>161.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32074</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTBRISON</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Commune de Cluny</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>142.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PDMDEP-31045</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PDMDEP-30335</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ALENCON</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PDMDEP-31360</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PDMDEP-31328</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LARMOR PLAGE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Migration de GEODP-Placier simple</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>42.15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PDMDEP-34466</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Commune de La Flèche</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier et ODP</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>895</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PDMDEP-34345</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Commune de Chalons-sur-Saone</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Achat nouveau PAX A920</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PDMDEP-34258</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VIENNE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration Placier et ODP </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2127.2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>9623.1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PDMDEP-34216</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHATEAUGIRON</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>525</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VILLE DE VANNES</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PDMDEP-33991</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COMMUNE DE QUIMPERLE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>510</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PDMDEP-33850</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Commune de Nans les Pins</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>680</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PDMDEP-33616</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MORLAIX</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1616</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PDMDEP-33605</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Commune de Trets</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1017.5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PDMDEP-33401</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTBELIARD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PDMDEP-33245</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LODEVE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Migracier activité Placier vers Geodp V2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PDMDEP-33177</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Commune de Bonneville</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PDMDEP-32974</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>COMMUNE DU PONTET</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier 2/2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PDMDEP-32340</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PDMDEP-32095</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Placier</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PDMDEP-31917</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Commune de GUINGAMP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>588</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PDMDEP-29608</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>669.38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>COMMUNE D'ANTIBES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1294.22</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>647.11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PDMDEP-31468</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>416.48</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>208.24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PDMDEP-29625</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>159.38</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VILLE DE CHALON SUR SAONE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>120.78</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PDMDEP-34654</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PDMDEP-34499</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CLICHY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1892</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PDMDEP-34235</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DIJON METROPOLE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GRC + Connecteur</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>4536</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PDMDEP-33944</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Commune de Thionville</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PDMDEP-33833</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PDMDEP-33808</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PDMDEP-33475</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COMMUNE D AUCH</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FDS Facture LiS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PDMDEP-33390</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>514.2</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>557.14</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GRAND DAX</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Interface Pastell</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PDMDEP-31197</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>COMMUNE D HENDAYE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Commune de Mouscron (BE)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commune de Macon </t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1662</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PDMDEP-33073</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LONGWY</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1207</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mise en service + WFS + AME</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>1030.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PDMDEP-30197</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pastell</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>690</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>586.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PDMDEP-31951</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PDMDEP-33955</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Commune de Colmar</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PDMDEP-33745</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>UPSELL PASTELL + DA DPA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PDMDEP-33232</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>21 crédits d'heure</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>625</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PDMDEP-32990</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Interface Civil net finance avec Littéralis</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PDMDEP-32268</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CA DU NIORTAIS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Modélisation</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PDMDEP-31971</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU LOT -CD46</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL GÉNÉRAL</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>61735.89</v>
+      </c>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="7" t="n">
+        <v>10014.31</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>33918.45</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4953.72</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>8564.9</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>3190.7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>14522.04</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1804.89</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>3768.5</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>962</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>38648.95</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>5018.72</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>23086.94</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>4995.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/previsionnel_2026.xlsx
+++ b/previsionnel_2026.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Récap" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Juillet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Août" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Septembre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -528,6 +529,22 @@
       </c>
       <c r="D5" s="3" t="n">
         <v>10014.31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>46991.99</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>6009.96</v>
       </c>
     </row>
   </sheetData>
@@ -6274,4 +6291,2253 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Prévisionnel pondéré — Septembre 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Capturé le 01/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Ticket CA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Niveau de confiance</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PDMDEP-34117</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMMUNE DU PUY EN VELAY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier + migration ODP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>707</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PDMDEP-33272</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CAPBRETON</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PDMDEP-28310</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Migration GEODP2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>362.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PDMDEP-32470</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NANTES METROPOLE - VDC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2335</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Basse</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>350.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PDMDEP-31658</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MAIRIE DE GUILLESTRE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GeoDP Placier</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>172.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PDMDEP-32002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Commune de Cluny</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>142.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31045</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PDMDEP-30335</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ALENCON</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31360</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34825</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ville de Bourges</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier et ODP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2419</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34258</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VIENNE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration Placier et ODP </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2127.2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>9623.1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PDMDEP-34216</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHATEAUGIRON</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>525</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VILLE DE VANNES</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PDMDEP-33991</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COMMUNE DE QUIMPERLE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>510</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PDMDEP-33401</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTBELIARD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PDMDEP-33245</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LODEVE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Migracier activité Placier vers Geodp V2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PDMDEP-33177</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Commune de Bonneville</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PDMDEP-32340</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PDMDEP-32095</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Placier</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PDMDEP-31917</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Commune de GUINGAMP</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>588</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PDMDEP-29608</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>669.38</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PDMDEP-29625</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>159.38</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VILLE DE CHALON SUR SAONE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>120.78</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PDMDEP-34235</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DIJON METROPOLE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GRC + Connecteur</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>4536</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PDMDEP-33944</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Commune de Thionville</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PDMDEP-33808</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PDMDEP-33475</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COMMUNE D AUCH</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FDS Facture LiS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>557.14</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GRAND DAX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Interface Pastell</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PDMDEP-31197</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COMMUNE D HENDAYE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Commune de Mouscron (BE)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commune de Macon </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GEODP Placier</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1662</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PDMDEP-33073</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LONGWY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1207</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mise en service + WFS + AME</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>1030.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PDMDEP-30197</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pastell</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>690</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>586.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PDMDEP-31951</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Haute</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PDMDEP-34979</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PDMDEP-33955</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Commune de Colmar</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PDMDEP-33745</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>UPSELL PASTELL + DA DPA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PDMDEP-33232</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21 crédits d'heure</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>625</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PDMDEP-32990</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Interface Civil net finance avec Littéralis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PDMDEP-32268</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CA DU NIORTAIS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Modélisation</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PDMDEP-31971</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU LOT -CD46</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Non planifié</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL GÉNÉRAL</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>46991.99</v>
+      </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="7" t="n">
+        <v>6009.96</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>9664.9</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3190.7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>23728.95</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1804.72</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>9122.639999999999</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>949.54</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>3768.5</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>(non assigné)</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>707</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Sous-totaux par solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Prévision brute (€)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Prévision pondérée (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>28204.45</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1869.72</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>18787.54</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>4140.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>